--- a/data/trans_orig/P36B06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2007</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>38919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>44089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>73482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76835</t>
+          <t>77143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138550</t>
+          <t>143175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>185895</t>
+          <t>190077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146797</t>
+          <t>146165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194647</t>
+          <t>195959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>301252</t>
+          <t>306377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>367336</t>
+          <t>370013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218236</t>
+          <t>214293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270495</t>
+          <t>268822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275184</t>
+          <t>277376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>337338</t>
+          <t>337067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>507689</t>
+          <t>506432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587787</t>
+          <t>587956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>517497</t>
+          <t>522915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>581107</t>
+          <t>585924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>754933</t>
+          <t>754791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>825239</t>
+          <t>821577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1296853</t>
+          <t>1292089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1394270</t>
+          <t>1388192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>61613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>75666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113781</t>
+          <t>113529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83026</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123653</t>
+          <t>122699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>48472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>80912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142861</t>
+          <t>141457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192364</t>
+          <t>194436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>236012</t>
+          <t>234430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>294385</t>
+          <t>295526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189744</t>
+          <t>188158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244360</t>
+          <t>243158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>438560</t>
+          <t>438822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>517349</t>
+          <t>523751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>508582</t>
+          <t>507452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>586643</t>
+          <t>584995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399242</t>
+          <t>399049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>471269</t>
+          <t>467809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>922604</t>
+          <t>936986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1026150</t>
+          <t>1041834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689974</t>
+          <t>693440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>770634</t>
+          <t>776804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>788359</t>
+          <t>787316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>868728</t>
+          <t>867682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507252</t>
+          <t>1502313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1614688</t>
+          <t>1614914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>70233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107336</t>
+          <t>106320</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>74945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125867</t>
+          <t>126976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171953</t>
+          <t>171654</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>135082</t>
+          <t>133972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177859</t>
+          <t>178808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110069</t>
+          <t>110938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148885</t>
+          <t>148596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255545</t>
+          <t>256822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>315943</t>
+          <t>318413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244469</t>
+          <t>244337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292993</t>
+          <t>293554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247011</t>
+          <t>249228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>291005</t>
+          <t>290334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501989</t>
+          <t>506967</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>570126</t>
+          <t>568366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59466</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48722</t>
+          <t>47929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>80331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116020</t>
+          <t>114936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160599</t>
+          <t>161032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>161648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214272</t>
+          <t>214246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93962</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133633</t>
+          <t>135217</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266037</t>
+          <t>269552</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>332657</t>
+          <t>338832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>476305</t>
+          <t>472696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>558543</t>
+          <t>557305</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408678</t>
+          <t>408221</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>488176</t>
+          <t>486088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>905375</t>
+          <t>908929</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1021589</t>
+          <t>1021166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>898465</t>
+          <t>892922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1003879</t>
+          <t>998289</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>820126</t>
+          <t>815240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>925708</t>
+          <t>917146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1748328</t>
+          <t>1745564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1890419</t>
+          <t>1893657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1487611</t>
+          <t>1492144</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1606903</t>
+          <t>1611346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1826413</t>
+          <t>1830932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1944171</t>
+          <t>1941798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3350941</t>
+          <t>3358261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3517571</t>
+          <t>3518832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2012</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46449</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>41468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65539</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70636</t>
+          <t>70922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106907</t>
+          <t>107555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62552</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97047</t>
+          <t>97620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142179</t>
+          <t>143455</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>192612</t>
+          <t>192819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149438</t>
+          <t>148047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198016</t>
+          <t>197951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154096</t>
+          <t>155648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206735</t>
+          <t>208429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319376</t>
+          <t>319022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391678</t>
+          <t>390175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>644847</t>
+          <t>644428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>701205</t>
+          <t>703887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1000073</t>
+          <t>997445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1060815</t>
+          <t>1058532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1663915</t>
+          <t>1665513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1748961</t>
+          <t>1750611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>63021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59176</t>
+          <t>59618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72064</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>112523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>58155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94378</t>
+          <t>93587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43970</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>76183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108785</t>
+          <t>110406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157405</t>
+          <t>157784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>213337</t>
+          <t>212364</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269393</t>
+          <t>268204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143896</t>
+          <t>143295</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195489</t>
+          <t>194787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>367264</t>
+          <t>366399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>443916</t>
+          <t>446863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>463331</t>
+          <t>463538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>543390</t>
+          <t>545876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377939</t>
+          <t>381264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449127</t>
+          <t>453546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>860283</t>
+          <t>862160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>966917</t>
+          <t>970999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1053671</t>
+          <t>1057127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143016</t>
+          <t>1147588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1022712</t>
+          <t>1025177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1105546</t>
+          <t>1108866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,47 +4875,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>63,31%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2169043</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2107080</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2228991</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>58,39%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>63,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2169043</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2106682</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2230671</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>58,39%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73188</t>
+          <t>72459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67155</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103147</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>114671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156042</t>
+          <t>158249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86725</t>
+          <t>87572</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125492</t>
+          <t>127941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214569</t>
+          <t>211164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>271159</t>
+          <t>268194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240036</t>
+          <t>235462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286416</t>
+          <t>284605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284448</t>
+          <t>288377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329113</t>
+          <t>331285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539758</t>
+          <t>544564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>603316</t>
+          <t>607434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57830</t>
+          <t>57995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92525</t>
+          <t>93174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>52242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87382</t>
+          <t>87686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116521</t>
+          <t>120391</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167760</t>
+          <t>168251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>133214</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74845</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116849</t>
+          <t>118383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176497</t>
+          <t>176468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237267</t>
+          <t>235035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>348386</t>
+          <t>349742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>422638</t>
+          <t>424600</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>242029</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306986</t>
+          <t>304900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607698</t>
+          <t>609970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708080</t>
+          <t>712553</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>758526</t>
+          <t>758813</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>860723</t>
+          <t>863970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>653268</t>
+          <t>657260</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>750869</t>
+          <t>748385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1442532</t>
+          <t>1439597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1582811</t>
+          <t>1579395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1976915</t>
+          <t>1979773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2097866</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2350198</t>
+          <t>2356245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2464748</t>
+          <t>2464064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4362512</t>
+          <t>4368919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4533664</t>
+          <t>4533307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2016</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>40096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>57401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90731</t>
+          <t>90204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93537</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126496</t>
+          <t>127121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174164</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189054</t>
+          <t>189353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237284</t>
+          <t>237404</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222392</t>
+          <t>219556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>277225</t>
+          <t>278981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>433058</t>
+          <t>428778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503923</t>
+          <t>503213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402126</t>
+          <t>402354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455906</t>
+          <t>457393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597826</t>
+          <t>598789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>660487</t>
+          <t>661522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1021851</t>
+          <t>1018500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1100015</t>
+          <t>1097417</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45944</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>80353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93563</t>
+          <t>92262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>135186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>71222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109679</t>
+          <t>109458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58805</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91868</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>139675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190678</t>
+          <t>190304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286177</t>
+          <t>287375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>352575</t>
+          <t>354073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224406</t>
+          <t>221717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283526</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>524820</t>
+          <t>527405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>613909</t>
+          <t>615772</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>601773</t>
+          <t>599861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>687894</t>
+          <t>686848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>552038</t>
+          <t>554088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>635568</t>
+          <t>633399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1179656</t>
+          <t>1176180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1295122</t>
+          <t>1299130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914122</t>
+          <t>915739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1009504</t>
+          <t>1007368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>966396</t>
+          <t>971713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058253</t>
+          <t>1061524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1906366</t>
+          <t>1904453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2037715</t>
+          <t>2035710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>52944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83157</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55979</t>
+          <t>55700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>86898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114923</t>
+          <t>113515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158205</t>
+          <t>156929</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123475</t>
+          <t>122204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>164905</t>
+          <t>164682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111807</t>
+          <t>111697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151581</t>
+          <t>151614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>245668</t>
+          <t>247136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>305668</t>
+          <t>302713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282259</t>
+          <t>280632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332126</t>
+          <t>331527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299624</t>
+          <t>299804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345648</t>
+          <t>344097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601343</t>
+          <t>598414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>667171</t>
+          <t>665947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>68971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108969</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89285</t>
+          <t>89401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134029</t>
+          <t>134150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186368</t>
+          <t>183698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108902</t>
+          <t>107484</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156778</t>
+          <t>154355</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95781</t>
+          <t>96015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136474</t>
+          <t>139190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215964</t>
+          <t>212421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>279016</t>
+          <t>275364</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>417601</t>
+          <t>416926</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>499909</t>
+          <t>499378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>360243</t>
+          <t>365985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>436457</t>
+          <t>437375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>804489</t>
+          <t>804161</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>918710</t>
+          <t>912027</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>947817</t>
+          <t>947415</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1059218</t>
+          <t>1061438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>921329</t>
+          <t>922860</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1029231</t>
+          <t>1029401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1892303</t>
+          <t>1898498</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2052108</t>
+          <t>2053258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1637535</t>
+          <t>1638086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1754006</t>
+          <t>1754324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1905042</t>
+          <t>1905204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2028869</t>
+          <t>2018774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3576894</t>
+          <t>3574931</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3749524</t>
+          <t>3752525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27516</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38919</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>73529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>49969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77143</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116884</t>
+          <t>115221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143175</t>
+          <t>141172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>190077</t>
+          <t>189718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>195959</t>
+          <t>195637</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>306377</t>
+          <t>301573</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>370013</t>
+          <t>367928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>214293</t>
+          <t>214928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268822</t>
+          <t>268781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277376</t>
+          <t>274454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>337067</t>
+          <t>336711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>506432</t>
+          <t>508013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587956</t>
+          <t>588949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>522915</t>
+          <t>517937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585924</t>
+          <t>580468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>754791</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>821577</t>
+          <t>822761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292089</t>
+          <t>1291950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1388192</t>
+          <t>1387640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>60933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>34442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>62139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75666</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113529</t>
+          <t>112403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84710</t>
+          <t>82434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122699</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48472</t>
+          <t>48001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80912</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141457</t>
+          <t>140277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194436</t>
+          <t>193411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>234430</t>
+          <t>232927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295526</t>
+          <t>293435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188158</t>
+          <t>189319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243158</t>
+          <t>242710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>438822</t>
+          <t>435479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>523751</t>
+          <t>520020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>507452</t>
+          <t>507526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>584995</t>
+          <t>590463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399049</t>
+          <t>397856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>467809</t>
+          <t>469259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>936986</t>
+          <t>930945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1041834</t>
+          <t>1040280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693440</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>776804</t>
+          <t>772265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>787316</t>
+          <t>787368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>867682</t>
+          <t>864153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502313</t>
+          <t>1496827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1614914</t>
+          <t>1615662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53198</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70233</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106320</t>
+          <t>108721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74945</t>
+          <t>76149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126976</t>
+          <t>125810</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171654</t>
+          <t>171747</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>133972</t>
+          <t>134157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178808</t>
+          <t>179274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110938</t>
+          <t>114167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148596</t>
+          <t>150459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>256822</t>
+          <t>258303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318413</t>
+          <t>317155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244337</t>
+          <t>242517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293554</t>
+          <t>291770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249228</t>
+          <t>245290</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>290334</t>
+          <t>289654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506967</t>
+          <t>505443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568366</t>
+          <t>572456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58330</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80331</t>
+          <t>80118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114936</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161032</t>
+          <t>162167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161648</t>
+          <t>160402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214246</t>
+          <t>214738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135217</t>
+          <t>135575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269552</t>
+          <t>269154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>338832</t>
+          <t>336673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>472696</t>
+          <t>475677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>557305</t>
+          <t>560415</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408221</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>486088</t>
+          <t>482843</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>908929</t>
+          <t>907512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1021166</t>
+          <t>1025588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>892922</t>
+          <t>895002</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>998289</t>
+          <t>995578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>815240</t>
+          <t>825229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>917146</t>
+          <t>919862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1745564</t>
+          <t>1740254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1893657</t>
+          <t>1886784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1492144</t>
+          <t>1499276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1611346</t>
+          <t>1612942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1830932</t>
+          <t>1825433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1941798</t>
+          <t>1937002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3358261</t>
+          <t>3361931</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3518832</t>
+          <t>3515549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25760</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>40989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>64874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70922</t>
+          <t>71740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107555</t>
+          <t>106759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97620</t>
+          <t>97849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>143455</t>
+          <t>140959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>192819</t>
+          <t>190355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148047</t>
+          <t>150004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197951</t>
+          <t>200390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155648</t>
+          <t>158917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208429</t>
+          <t>211490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319022</t>
+          <t>317426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390175</t>
+          <t>392302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>644428</t>
+          <t>645904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>703887</t>
+          <t>703784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>997445</t>
+          <t>995928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1058532</t>
+          <t>1060551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1665513</t>
+          <t>1664976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1750611</t>
+          <t>1755171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63021</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>74101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112523</t>
+          <t>114605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58155</t>
+          <t>56699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93587</t>
+          <t>92774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76183</t>
+          <t>76606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110406</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157784</t>
+          <t>159148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212364</t>
+          <t>213899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>268204</t>
+          <t>269797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143295</t>
+          <t>141362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194787</t>
+          <t>191663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>366399</t>
+          <t>365734</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>446863</t>
+          <t>448673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>463538</t>
+          <t>459680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>545876</t>
+          <t>539083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>379380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453546</t>
+          <t>452629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>862160</t>
+          <t>868281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>970999</t>
+          <t>979084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1057127</t>
+          <t>1057959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147588</t>
+          <t>1149451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025177</t>
+          <t>1027726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1108866</t>
+          <t>1112345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2107080</t>
+          <t>2101354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2228991</t>
+          <t>2228535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>42625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>73627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67118</t>
+          <t>67748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104997</t>
+          <t>105597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114671</t>
+          <t>114950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158249</t>
+          <t>155480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>88557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>126611</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>211164</t>
+          <t>211833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>268194</t>
+          <t>269952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235462</t>
+          <t>238633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284605</t>
+          <t>284408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288377</t>
+          <t>285940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331285</t>
+          <t>330074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544564</t>
+          <t>541434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>607434</t>
+          <t>605896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93174</t>
+          <t>93162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52242</t>
+          <t>51711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87686</t>
+          <t>87783</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120391</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168251</t>
+          <t>169277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90733</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133214</t>
+          <t>133359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>117819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176468</t>
+          <t>177336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>235035</t>
+          <t>235079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>349742</t>
+          <t>345952</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>424600</t>
+          <t>423220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>240905</t>
+          <t>239522</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>304900</t>
+          <t>302360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>609970</t>
+          <t>605200</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>712553</t>
+          <t>703308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>758813</t>
+          <t>756907</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>863970</t>
+          <t>862509</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>657260</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>748385</t>
+          <t>751852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1439597</t>
+          <t>1442817</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1579395</t>
+          <t>1581720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1979773</t>
+          <t>1979383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2099370</t>
+          <t>2097728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2356245</t>
+          <t>2347613</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2464064</t>
+          <t>2464027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4368919</t>
+          <t>4369102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4533307</t>
+          <t>4530189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40096</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36106</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>58598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90204</t>
+          <t>89472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59356</t>
+          <t>59603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94108</t>
+          <t>94750</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127121</t>
+          <t>126692</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174682</t>
+          <t>175207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189353</t>
+          <t>189742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237404</t>
+          <t>240209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>222269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278981</t>
+          <t>280809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>428778</t>
+          <t>432168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503213</t>
+          <t>504894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402354</t>
+          <t>400717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457393</t>
+          <t>454317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598789</t>
+          <t>596638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>661522</t>
+          <t>662438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018500</t>
+          <t>1017821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1097417</t>
+          <t>1100280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,09%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80353</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66553</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,47 +7382,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>112170</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>91569</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>136136</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>112170</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>92262</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>135186</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>72642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109458</t>
+          <t>111327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>57376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93689</t>
+          <t>91327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139675</t>
+          <t>140718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190304</t>
+          <t>191808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287375</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>354073</t>
+          <t>355394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221717</t>
+          <t>223891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>284811</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>527405</t>
+          <t>526272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>615772</t>
+          <t>616141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>599861</t>
+          <t>605026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>686848</t>
+          <t>691739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>554088</t>
+          <t>549612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>633399</t>
+          <t>634148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1176180</t>
+          <t>1181265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1299130</t>
+          <t>1299987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915739</t>
+          <t>913300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1007368</t>
+          <t>1005155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971713</t>
+          <t>967313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1061524</t>
+          <t>1058172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904453</t>
+          <t>1903849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2035710</t>
+          <t>2038254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18154</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>27948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>31723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27315</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>27050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52944</t>
+          <t>51174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>50762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>84533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86898</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113515</t>
+          <t>114660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156929</t>
+          <t>161216</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122204</t>
+          <t>122392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>164682</t>
+          <t>166487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111697</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151614</t>
+          <t>152205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>247136</t>
+          <t>244650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302713</t>
+          <t>304597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280632</t>
+          <t>280668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331527</t>
+          <t>329720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299804</t>
+          <t>300404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344097</t>
+          <t>345071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>598414</t>
+          <t>596589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>665947</t>
+          <t>661537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109810</t>
+          <t>109386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89401</t>
+          <t>92083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134150</t>
+          <t>134245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183698</t>
+          <t>184862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107484</t>
+          <t>107865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>152472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96015</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139190</t>
+          <t>136636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212421</t>
+          <t>216618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275364</t>
+          <t>279765</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>416926</t>
+          <t>414795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>499378</t>
+          <t>499643</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>365985</t>
+          <t>363750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>437375</t>
+          <t>435231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>804161</t>
+          <t>804751</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>912027</t>
+          <t>914569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>947415</t>
+          <t>952193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1061438</t>
+          <t>1058762</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>922860</t>
+          <t>924794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1029401</t>
+          <t>1026918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1898498</t>
+          <t>1902838</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2053258</t>
+          <t>2048957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1638086</t>
+          <t>1633907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1754324</t>
+          <t>1753841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1905204</t>
+          <t>1909704</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2018774</t>
+          <t>2025974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3574931</t>
+          <t>3574507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3752525</t>
+          <t>3748198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
